--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>古賀</t>
+          <t>岡野</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -790,7 +790,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>平井</t>
+          <t>中村</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>岡野</t>
+          <t>和久</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>副島</t>
+          <t>倉光</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>中村</t>
+          <t>山内</t>
         </is>
       </c>
       <c r="J6" s="3" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>長本</t>
+          <t>副島</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>和久</t>
+          <t>平井</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -850,7 +850,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>倉光</t>
+          <t>土井下</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
@@ -858,33 +858,17 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>山内</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>栗原</t>
+          <t>大徳</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>原</t>
-        </is>
-      </c>
       <c r="D8" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>土井下</t>
+          <t>菊池</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
@@ -892,49 +876,17 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>大徳</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>髙橋</t>
+          <t>古賀</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>阿部</t>
-        </is>
-      </c>
       <c r="D9" s="3" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>菊池</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>江口</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>黒田</t>
+          <t>大山</t>
         </is>
       </c>
     </row>
@@ -944,7 +896,17 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>宮口</t>
+          <t>原</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>長本</t>
         </is>
       </c>
     </row>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -559,11 +559,7 @@
           <t>佐藤</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>髙橋</t>
-        </is>
-      </c>
+      <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>副島</t>
@@ -584,11 +580,7 @@
           <t>菊池</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>江口</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>田代</t>
@@ -601,11 +593,7 @@
           <t>山内</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>黒田</t>
-        </is>
-      </c>
+      <c r="B6" s="3" t="n"/>
       <c r="C6" s="3" t="inlineStr">
         <is>
           <t>馬渡</t>
@@ -616,21 +604,9 @@
           <t>古賀</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>栗原</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>阿部</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>宮口</t>
-        </is>
-      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
     </row>
     <row r="8">
@@ -939,15 +915,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>長本・古賀</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>館長息子・倉光</t>
+          <t>原・中嶋</t>
         </is>
       </c>
     </row>
@@ -965,7 +933,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>黒田・大徳</t>
+          <t>伊地知・平井</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
@@ -973,15 +941,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>原・髙橋</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>中村・山内</t>
+          <t>佐藤・大徳</t>
         </is>
       </c>
     </row>
@@ -999,7 +959,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>伊地知・平井</t>
+          <t>土井下・平野</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
@@ -1007,7 +967,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>中嶋・江口</t>
+          <t>館長息子・倉光</t>
         </is>
       </c>
     </row>
@@ -1025,7 +985,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>土井下・平野</t>
+          <t>和久・副島</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
@@ -1033,7 +993,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>阿部・宮口</t>
+          <t>中村・山内</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1011,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>和久・副島</t>
+          <t>長本・古賀</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
@@ -1059,7 +1019,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>佐藤・栗原</t>
+          <t>大山・（相手未定）</t>
         </is>
       </c>
     </row>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>小野</t>
+          <t>小野(亮太)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>原</t>
+          <t>原(潤一郎)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>倉光</t>
+          <t>土井下</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
@@ -826,7 +826,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>土井下</t>
+          <t>菊池</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
@@ -835,6 +835,14 @@
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>大徳</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>一期崎</t>
         </is>
       </c>
     </row>
@@ -844,7 +852,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>菊池</t>
+          <t>大山</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
@@ -853,6 +861,14 @@
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>古賀</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>北原</t>
         </is>
       </c>
     </row>
@@ -862,7 +878,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>大山</t>
+          <t>原</t>
         </is>
       </c>
     </row>
@@ -871,16 +887,6 @@
         <v>8</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>原</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="D11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>長本</t>
         </is>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乗車割" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チーム・ペア分け" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チーム分け(団体戦)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教科対抗戦" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,7 +46,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +78,26 @@
         <fgColor rgb="00B6E3A0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFB3B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0099CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9B3FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -96,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -116,6 +137,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -627,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -892,143 +928,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ペア分け（ミックスダブルス戦）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>社長・館長</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>岡野・菊池</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>原・中嶋</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>黒岩夫婦</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>伊地知・平井</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>佐藤・大徳</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>日高夫婦</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>土井下・平野</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>館長息子・倉光</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>小野夫婦</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>和久・副島</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>中村・山内</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>高本夫婦</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>長本・古賀</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>大山・（相手未定）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="G2:H2"/>
@@ -1038,4 +937,422 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>教科・事務対抗戦（6チーム）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>国語</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>社会</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>理科</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n"/>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>事務</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>馬渡</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>小野(亮太)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>藤田</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>平野</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>土井下</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>神田</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>長本</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>伊地知</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>岡野</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>大山</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>中村</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>田代</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>副島</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>平井</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>中嶋</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>和久</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>原(潤一郎)</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>高本</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>日高</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>古賀</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>山内</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>菊池</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>佐藤</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>黒岩</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>谷川</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="P9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>大徳</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="P10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>一期崎</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="P11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>小野(多恵)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="P12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>北原</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="P13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>原(由実子)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="P14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>山本</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>5名</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>5名</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>4名</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>3名</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>3名</t>
+        </is>
+      </c>
+      <c r="P15" s="13" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>11名</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -519,17 +519,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,104 +551,194 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>原(潤一郎)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>大山</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>平井</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>小野(亮太)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>高本</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>小野(亮太)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>伊地知</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>日高</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>山本</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>伊地知</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>原(潤一郎)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>大山</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>神田
 (現地集合)</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>タクシー</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>佐藤</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n"/>
+          <t>黒岩</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>土井下</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>副島</t>
+          <t>平野</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>岡野</t>
+          <t>ご家族</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>中嶋</t>
+          <t>ご家族</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>菊池</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n"/>
+          <t>馬渡</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>ご家族</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>ご家族</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>田代</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>社長</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>山内</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
+          <t>長本</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>北原</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>馬渡</t>
+          <t>佐藤</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>古賀</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
+          <t>中村</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>岡野</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>中嶋</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>館長</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>山内</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>古賀</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>副島</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>和久</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>事務</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>※神田先生の車は田代先生のみ。ヒルトップへ直接向かい、現地集合。</t>
         </is>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -580,7 +580,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
@@ -607,7 +607,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -852,13 +851,13 @@
       <c r="L8" s="6" t="n"/>
       <c r="M8" s="6" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="52" horizontalDpi="0" verticalDpi="0"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="52" fitToHeight="1" fitToWidth="1" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -866,22 +865,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
     <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="3" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
@@ -939,7 +938,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>小野先生</t>
+          <t>小野(亮太)先生</t>
         </is>
       </c>
       <c r="J3" s="6" t="n">
@@ -1067,7 +1066,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>原先生</t>
+          <t>原(潤一郎)先生</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
@@ -1122,12 +1121,28 @@
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>原(由実子)さん</t>
+        </is>
+      </c>
       <c r="D9" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
           <t>黒岩先生</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>小野(多恵)さん</t>
         </is>
       </c>
     </row>
@@ -1138,8 +1153,9 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1147,7 +1163,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
@@ -1178,7 +1194,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -1460,7 +1475,8 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="68" horizontalDpi="0" verticalDpi="0"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="68" fitToHeight="1" fitToWidth="1" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="13"/>
@@ -594,7 +594,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
@@ -660,24 +660,19 @@
           <t>山本先生</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
-        <is>
-          <t>原（由）さん</t>
-        </is>
-      </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>神田先生
 (現地)</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr">
+      <c r="K4" s="15" t="inlineStr">
         <is>
           <t>社長
 (現地)</t>
         </is>
       </c>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="L4" s="15" t="inlineStr">
         <is>
           <t>井上さん</t>
         </is>
@@ -696,7 +691,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>平野先生</t>
+          <t>佐藤先生</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -731,20 +726,15 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>ご家族１名</t>
+          <t>田代先生</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>田代先生</t>
+          <t>留美子さん</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>留美子さん</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>子ども３</t>
         </is>
@@ -763,7 +753,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>佐藤先生</t>
+          <t>原(由実子)さん</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -788,14 +778,9 @@
       </c>
       <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>菊池さん</t>
-        </is>
-      </c>
+      <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -808,7 +793,11 @@
           <t>一期崎さん</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>実優ちゃん</t>
+        </is>
+      </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>古賀先生</t>
@@ -819,7 +808,11 @@
           <t>副島先生</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>平野先生</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>北原先生</t>
@@ -830,7 +823,6 @@
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="6" t="n"/>
       <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="6" t="n"/>
@@ -839,7 +831,11 @@
           <t>小野(多)さん</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>菊池さん</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
@@ -849,7 +845,6 @@
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="n"/>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="13"/>
@@ -607,6 +607,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="21" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -657,7 +658,7 @@
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>山本先生</t>
+          <t>山本さん</t>
         </is>
       </c>
       <c r="J4" s="15" t="inlineStr">
@@ -674,14 +675,15 @@
       </c>
       <c r="L4" s="15" t="inlineStr">
         <is>
-          <t>井上さん</t>
+          <t>井上さん
+(現地)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>黒岩先生</t>
+          <t>黒岩</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -846,6 +848,7 @@
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="n"/>
     </row>
@@ -1087,7 +1090,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>山本先生</t>
+          <t>山本さん</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
@@ -1129,7 +1132,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>黒岩先生</t>
+          <t>黒岩</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
@@ -1189,6 +1192,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -1415,7 +1419,7 @@
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>山本先生</t>
+          <t>山本さん</t>
         </is>
       </c>
       <c r="P7" s="6" t="n">
@@ -1441,7 +1445,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>黒岩先生</t>
+          <t>黒岩</t>
         </is>
       </c>
       <c r="J8" s="6" t="n">

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -58,6 +58,38 @@
       <family val="3"/>
       <sz val="6"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="11">
@@ -173,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,6 +249,43 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -601,79 +670,114 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>互助会レクリエーション</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="18" t="n"/>
+      <c r="C1" s="18" t="n"/>
+      <c r="D1" s="18" t="n"/>
+      <c r="E1" s="18" t="n"/>
+      <c r="F1" s="18" t="n"/>
+      <c r="G1" s="18" t="n"/>
+      <c r="H1" s="18" t="n"/>
+      <c r="I1" s="18" t="n"/>
+      <c r="J1" s="18" t="n"/>
+      <c r="K1" s="18" t="n"/>
+      <c r="L1" s="18" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="n"/>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="18" t="n"/>
+      <c r="H2" s="18" t="n"/>
+      <c r="I2" s="18" t="n"/>
+      <c r="J2" s="18" t="n"/>
+      <c r="K2" s="18" t="n"/>
+      <c r="L2" s="18" t="n"/>
+    </row>
     <row r="3" ht="21" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>乗車割</t>
         </is>
       </c>
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="18" t="n"/>
+      <c r="H3" s="18" t="n"/>
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="18" t="n"/>
+      <c r="K3" s="18" t="n"/>
+      <c r="L3" s="18" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>原(潤)先生</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>大山先生</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>平井先生</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>小野(亮)先生</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>高本先生</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>伊地知先生</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>和久先生</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>日高先生</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>山本さん</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>神田先生
 (現地)</t>
         </is>
       </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="K4" s="20" t="inlineStr">
         <is>
           <t>社長
 (現地)</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr">
+      <c r="L4" s="20" t="inlineStr">
         <is>
           <t>井上さん
 (現地)</t>
@@ -681,176 +785,200 @@
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>黒岩</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>土井下先生</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>佐藤先生</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>ご家族３名</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>ご家族１名</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>馬渡先生</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>藤田館長</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>ご家族２名</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>ご家族２名</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>田代先生</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>留美子さん</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t>子ども３</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>長本先生</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>大徳さん</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>原(由実子)さん</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>中村先生</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>岡野先生</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>中嶋先生</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>修史くん</t>
         </is>
       </c>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="21" t="n"/>
+      <c r="J6" s="21" t="n"/>
+      <c r="K6" s="21" t="n"/>
+      <c r="L6" s="21" t="n"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>山内先生</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>一期崎さん</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>実優ちゃん</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>古賀先生</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>副島先生</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>平野先生</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>北原先生</t>
         </is>
       </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="21" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>小野(多)さん</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>菊池さん</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-    </row>
-    <row r="9"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="21" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="n"/>
+      <c r="L9" s="18" t="n"/>
+    </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="4" t="n"/>
+      <c r="A10" s="22" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="18" t="n"/>
+      <c r="L10" s="18" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -882,267 +1010,303 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>チーム分け（団体戦）</t>
         </is>
       </c>
+      <c r="B1" s="18" t="n"/>
+      <c r="C1" s="18" t="n"/>
+      <c r="D1" s="18" t="n"/>
+      <c r="E1" s="18" t="n"/>
+      <c r="F1" s="18" t="n"/>
+      <c r="G1" s="18" t="n"/>
+      <c r="H1" s="18" t="n"/>
+      <c r="I1" s="18" t="n"/>
+      <c r="J1" s="18" t="n"/>
+      <c r="K1" s="18" t="n"/>
     </row>
     <row r="2" ht="16.5" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>六本松</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>梅光園</t>
         </is>
       </c>
-      <c r="E2" s="16" t="n"/>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="26" t="inlineStr">
         <is>
           <t>高宮</t>
         </is>
       </c>
-      <c r="H2" s="16" t="n"/>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="H2" s="24" t="n"/>
+      <c r="I2" s="18" t="n"/>
+      <c r="J2" s="27" t="inlineStr">
         <is>
           <t>西新</t>
         </is>
       </c>
-      <c r="K2" s="16" t="n"/>
+      <c r="K2" s="24" t="n"/>
     </row>
     <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="6" t="n">
+      <c r="A3" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>日高先生</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>藤田館長</t>
         </is>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>小野(亮太)先生</t>
         </is>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="21" t="inlineStr">
         <is>
           <t>高本先生</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>平野先生</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>土井下先生</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t>佐藤先生</t>
         </is>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="21" t="inlineStr">
         <is>
           <t>伊地知先生</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>岡野先生</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>菊池さん</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>中村先生</t>
         </is>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>中嶋先生</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>和久先生</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>大山先生</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>山内先生</t>
         </is>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>副島先生</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>平井先生</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>原(潤一郎)先生</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>古賀先生</t>
         </is>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>一期崎さん</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>山本さん</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>長本先生</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>大徳さん</t>
         </is>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>北原先生</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>原(由実子)さん</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>黒岩</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>小野(多恵)さん</t>
         </is>
       </c>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1186,280 +1350,348 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>教科・事務対抗戦（6チーム）</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="18" t="n"/>
+      <c r="C1" s="18" t="n"/>
+      <c r="D1" s="18" t="n"/>
+      <c r="E1" s="18" t="n"/>
+      <c r="F1" s="18" t="n"/>
+      <c r="G1" s="18" t="n"/>
+      <c r="H1" s="18" t="n"/>
+      <c r="I1" s="18" t="n"/>
+      <c r="J1" s="18" t="n"/>
+      <c r="K1" s="18" t="n"/>
+      <c r="L1" s="18" t="n"/>
+      <c r="M1" s="18" t="n"/>
+      <c r="N1" s="18" t="n"/>
+      <c r="O1" s="18" t="n"/>
+      <c r="P1" s="18" t="n"/>
+      <c r="Q1" s="18" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="n"/>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="18" t="n"/>
+      <c r="H2" s="18" t="n"/>
+      <c r="I2" s="18" t="n"/>
+      <c r="J2" s="18" t="n"/>
+      <c r="K2" s="18" t="n"/>
+      <c r="L2" s="18" t="n"/>
+      <c r="M2" s="18" t="n"/>
+      <c r="N2" s="18" t="n"/>
+      <c r="O2" s="18" t="n"/>
+      <c r="P2" s="18" t="n"/>
+      <c r="Q2" s="18" t="n"/>
+    </row>
     <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>国語</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="B3" s="24" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="E3" s="16" t="n"/>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="E3" s="24" t="n"/>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t>社会</t>
         </is>
       </c>
-      <c r="H3" s="16" t="n"/>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="H3" s="24" t="n"/>
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="27" t="inlineStr">
         <is>
           <t>理科</t>
         </is>
       </c>
-      <c r="K3" s="16" t="n"/>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="K3" s="24" t="n"/>
+      <c r="L3" s="18" t="n"/>
+      <c r="M3" s="31" t="inlineStr">
         <is>
           <t>英語</t>
         </is>
       </c>
-      <c r="N3" s="16" t="n"/>
-      <c r="P3" s="10" t="inlineStr">
+      <c r="N3" s="24" t="n"/>
+      <c r="O3" s="18" t="n"/>
+      <c r="P3" s="19" t="inlineStr">
         <is>
           <t>事務</t>
         </is>
       </c>
-      <c r="Q3" s="16" t="n"/>
+      <c r="Q3" s="24" t="n"/>
     </row>
     <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>馬渡先生</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>小野(亮太)先生</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t>藤田先生</t>
         </is>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="21" t="inlineStr">
         <is>
           <t>高本先生</t>
         </is>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="L4" s="18" t="n"/>
+      <c r="M4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t>土井下先生</t>
         </is>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="O4" s="18" t="n"/>
+      <c r="P4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="21" t="inlineStr">
         <is>
           <t>原(由実子)さん</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>長本先生</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>伊地知先生</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>岡野先生</t>
         </is>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>平野先生</t>
         </is>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="L5" s="18" t="n"/>
+      <c r="M5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t>中村先生</t>
         </is>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="O5" s="18" t="n"/>
+      <c r="P5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>菊池さん</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>副島先生</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>平井先生</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>中嶋先生</t>
         </is>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>和久先生</t>
         </is>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="L6" s="18" t="n"/>
+      <c r="M6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N6" s="6" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t>原(潤一郎)先生</t>
         </is>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="O6" s="18" t="n"/>
+      <c r="P6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="21" t="inlineStr">
         <is>
           <t>大徳さん</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>日高先生</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>古賀先生</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>山内先生</t>
         </is>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>大山先生</t>
         </is>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="L7" s="18" t="n"/>
+      <c r="M7" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>山本さん</t>
         </is>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="O7" s="18" t="n"/>
+      <c r="P7" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>一期崎さん</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>佐藤先生</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>黒岩</t>
         </is>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>北原先生</t>
         </is>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="L8" s="18" t="n"/>
+      <c r="M8" s="18" t="n"/>
+      <c r="N8" s="18" t="n"/>
+      <c r="O8" s="18" t="n"/>
+      <c r="P8" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="21" t="inlineStr">
         <is>
           <t>小野(多恵)さん</t>
         </is>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>一期崎さん</t>
+          <t>一期﨑さん</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -1032,28 +1032,28 @@
           <t>六本松</t>
         </is>
       </c>
-      <c r="B2" s="24" t="n"/>
+      <c r="B2" s="16" t="n"/>
       <c r="C2" s="18" t="n"/>
       <c r="D2" s="25" t="inlineStr">
         <is>
           <t>梅光園</t>
         </is>
       </c>
-      <c r="E2" s="24" t="n"/>
+      <c r="E2" s="16" t="n"/>
       <c r="F2" s="18" t="n"/>
       <c r="G2" s="26" t="inlineStr">
         <is>
           <t>高宮</t>
         </is>
       </c>
-      <c r="H2" s="24" t="n"/>
+      <c r="H2" s="16" t="n"/>
       <c r="I2" s="18" t="n"/>
       <c r="J2" s="27" t="inlineStr">
         <is>
           <t>西新</t>
         </is>
       </c>
-      <c r="K2" s="24" t="n"/>
+      <c r="K2" s="16" t="n"/>
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="21" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="K7" s="21" t="inlineStr">
         <is>
-          <t>一期崎さん</t>
+          <t>一期﨑さん</t>
         </is>
       </c>
     </row>
@@ -1305,8 +1305,14 @@
         </is>
       </c>
       <c r="I9" s="18" t="n"/>
-      <c r="J9" s="18" t="n"/>
-      <c r="K9" s="18" t="n"/>
+      <c r="J9" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>馬渡先生</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1397,42 +1403,42 @@
           <t>国語</t>
         </is>
       </c>
-      <c r="B3" s="24" t="n"/>
+      <c r="B3" s="16" t="n"/>
       <c r="C3" s="18" t="n"/>
       <c r="D3" s="29" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="E3" s="24" t="n"/>
+      <c r="E3" s="16" t="n"/>
       <c r="F3" s="18" t="n"/>
       <c r="G3" s="30" t="inlineStr">
         <is>
           <t>社会</t>
         </is>
       </c>
-      <c r="H3" s="24" t="n"/>
+      <c r="H3" s="16" t="n"/>
       <c r="I3" s="18" t="n"/>
       <c r="J3" s="27" t="inlineStr">
         <is>
           <t>理科</t>
         </is>
       </c>
-      <c r="K3" s="24" t="n"/>
+      <c r="K3" s="16" t="n"/>
       <c r="L3" s="18" t="n"/>
       <c r="M3" s="31" t="inlineStr">
         <is>
           <t>英語</t>
         </is>
       </c>
-      <c r="N3" s="24" t="n"/>
+      <c r="N3" s="16" t="n"/>
       <c r="O3" s="18" t="n"/>
       <c r="P3" s="19" t="inlineStr">
         <is>
           <t>事務</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="n"/>
+      <c r="Q3" s="16" t="n"/>
     </row>
     <row r="4" ht="16.5" customHeight="1">
       <c r="A4" s="21" t="n">
@@ -1650,7 +1656,7 @@
       </c>
       <c r="Q7" s="21" t="inlineStr">
         <is>
-          <t>一期崎さん</t>
+          <t>一期﨑さん</t>
         </is>
       </c>
     </row>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t>馬渡先生</t>
+          <t>中嶋先生</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t>中嶋先生</t>
+          <t>平野先生</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -914,11 +914,7 @@
           <t>副島先生</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>平野先生</t>
-        </is>
-      </c>
+      <c r="F7" s="21" t="n"/>
       <c r="G7" s="21" t="inlineStr">
         <is>
           <t>北原先生</t>
@@ -1305,14 +1301,8 @@
         </is>
       </c>
       <c r="I9" s="18" t="n"/>
-      <c r="J9" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>馬渡先生</t>
-        </is>
-      </c>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1446,7 +1436,7 @@
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>馬渡先生</t>
+          <t>長本先生</t>
         </is>
       </c>
       <c r="C4" s="18" t="n"/>
@@ -1501,7 +1491,7 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>長本先生</t>
+          <t>副島先生</t>
         </is>
       </c>
       <c r="C5" s="18" t="n"/>
@@ -1556,7 +1546,7 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>副島先生</t>
+          <t>日高先生</t>
         </is>
       </c>
       <c r="C6" s="18" t="n"/>
@@ -1611,7 +1601,7 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>日高先生</t>
+          <t>佐藤先生</t>
         </is>
       </c>
       <c r="C7" s="18" t="n"/>
@@ -1661,14 +1651,8 @@
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>佐藤先生</t>
-        </is>
-      </c>
+      <c r="A8" s="18" t="n"/>
+      <c r="B8" s="18" t="n"/>
       <c r="C8" s="18" t="n"/>
       <c r="D8" s="21" t="n">
         <v>5</v>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乗車割" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チーム分け(団体戦)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教科対抗戦" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チーム分け(教室対抗戦)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教科事務対抗PK戦" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1008,7 +1008,7 @@
     <row r="1" ht="21" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>チーム分け（団体戦）</t>
+          <t>チーム分け（教室対抗戦）</t>
         </is>
       </c>
       <c r="B1" s="18" t="n"/>
@@ -1348,7 +1348,7 @@
     <row r="1" ht="21" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>教科・事務対抗戦（6チーム）</t>
+          <t>教科事務対抗PK戦（6チーム）</t>
         </is>
       </c>
       <c r="B1" s="18" t="n"/>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -989,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E3" s="21" t="inlineStr">
         <is>
-          <t>藤田館長</t>
+          <t>社長</t>
         </is>
       </c>
       <c r="F3" s="18" t="n"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>土井下先生</t>
+          <t>藤田館長</t>
         </is>
       </c>
       <c r="F4" s="18" t="n"/>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>菊池さん</t>
+          <t>土井下先生</t>
         </is>
       </c>
       <c r="F5" s="18" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>大山先生</t>
+          <t>菊池さん</t>
         </is>
       </c>
       <c r="F6" s="18" t="n"/>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>原(潤一郎)先生</t>
+          <t>大山先生</t>
         </is>
       </c>
       <c r="F7" s="18" t="n"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>長本先生</t>
+          <t>原(潤一郎)先生</t>
         </is>
       </c>
       <c r="F8" s="18" t="n"/>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>黒岩</t>
+          <t>長本先生</t>
         </is>
       </c>
       <c r="F9" s="18" t="n"/>
@@ -1303,6 +1303,16 @@
       <c r="I9" s="18" t="n"/>
       <c r="J9" s="18" t="n"/>
       <c r="K9" s="18" t="n"/>
+    </row>
+    <row r="10">
+      <c r="D10" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>黒岩</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1472,7 +1482,7 @@
       </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t>土井下先生</t>
+          <t>社長</t>
         </is>
       </c>
       <c r="O4" s="18" t="n"/>
@@ -1527,7 +1537,7 @@
       </c>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t>中村先生</t>
+          <t>土井下先生</t>
         </is>
       </c>
       <c r="O5" s="18" t="n"/>
@@ -1582,7 +1592,7 @@
       </c>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t>原(潤一郎)先生</t>
+          <t>中村先生</t>
         </is>
       </c>
       <c r="O6" s="18" t="n"/>
@@ -1637,7 +1647,7 @@
       </c>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t>山本さん</t>
+          <t>原(潤一郎)先生</t>
         </is>
       </c>
       <c r="O7" s="18" t="n"/>
@@ -1675,8 +1685,14 @@
         </is>
       </c>
       <c r="L8" s="18" t="n"/>
-      <c r="M8" s="18" t="n"/>
-      <c r="N8" s="18" t="n"/>
+      <c r="M8" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t>山本さん</t>
+        </is>
+      </c>
       <c r="O8" s="18" t="n"/>
       <c r="P8" s="21" t="n">
         <v>5</v>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乗車割" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チーム分け(教室対抗戦)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教科事務対抗PK戦" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="景品リスト" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -91,8 +92,27 @@
       <family val="3"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -144,8 +164,38 @@
         <fgColor rgb="FFD9B3FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -201,11 +251,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -285,6 +362,45 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="16" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1716,4 +1832,256 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" scale="68" fitToHeight="1" fitToWidth="1" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>景品リスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>賞</t>
+        </is>
+      </c>
+      <c r="C3" s="33" t="inlineStr">
+        <is>
+          <t>金額（円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>教室対抗戦</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>優勝（1位）</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="n"/>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="n"/>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="n"/>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>4位</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="39" t="n"/>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C8" s="41">
+        <f>SUM(C4:C7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>教科事務対抗PK戦</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>1位</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>2位</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>3位</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>4位</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="n"/>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>5位</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="39" t="n"/>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C14" s="41">
+        <f>SUM(C9:C13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>MVP（各教室）</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>六本松</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>梅光園</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="n"/>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>高宮</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="38" t="n"/>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>西新</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="39" t="n"/>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C19" s="41">
+        <f>SUM(C15:C18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="n"/>
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C20" s="46">
+        <f>C8+C14+C19</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="A15:A18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -1840,7 +1840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1855,6 +1855,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="33" t="inlineStr">
         <is>
@@ -1944,7 +1945,7 @@
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="10">
@@ -1955,7 +1956,7 @@
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>10000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="11">
@@ -1966,7 +1967,7 @@
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="12">
@@ -1977,7 +1978,7 @@
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="13">
@@ -1988,7 +1989,7 @@
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
@@ -2075,6 +2076,15 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A4:A7"/>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -1840,7 +1840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1855,7 +1855,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="33" t="inlineStr">
         <is>
@@ -1982,48 +1981,48 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="n"/>
+      <c r="A13" s="37" t="n"/>
       <c r="B13" s="35" t="inlineStr">
         <is>
           <t>5位</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="n"/>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>6位</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="39" t="n"/>
-      <c r="B14" s="40" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="39" t="n"/>
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="C14" s="41">
-        <f>SUM(C9:C13)</f>
+      <c r="C15" s="41">
+        <f>SUM(C9:C14)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>MVP（各教室）</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>六本松</t>
-        </is>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="37" t="n"/>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>梅光園</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
@@ -2034,7 +2033,7 @@
       <c r="A17" s="37" t="n"/>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>高宮</t>
+          <t>梅光園</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
@@ -2042,10 +2041,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="n"/>
+      <c r="A18" s="37" t="n"/>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>西新</t>
+          <t>高宮</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
@@ -2053,43 +2052,45 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="n"/>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="A19" s="38" t="n"/>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>西新</t>
+        </is>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="n"/>
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="C19" s="41">
-        <f>SUM(C15:C18)</f>
+      <c r="C20" s="41">
+        <f>SUM(C16:C19)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="44" t="n"/>
-      <c r="B20" s="45" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="44" t="n"/>
+      <c r="B21" s="45" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C20" s="46">
-        <f>C8+C14+C19</f>
+      <c r="C21" s="46">
+        <f>C8+C15+C20</f>
         <v/>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A9:A14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チーム分け(教室対抗戦)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教科事務対抗PK戦" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="景品リスト" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タイムスケジュール" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -111,8 +112,17 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <sz val="15"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -192,6 +202,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -282,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -401,6 +426,102 @@
     </xf>
     <xf numFmtId="3" fontId="14" fillId="16" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2095,4 +2216,437 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>タイムスケジュール（10:00開始・12:00終了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="63" t="inlineStr">
+        <is>
+          <t>開始</t>
+        </is>
+      </c>
+      <c r="B3" s="63" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="C3" s="63" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="D3" s="63" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E3" s="63" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="64" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B4" s="64" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C4" s="64" t="inlineStr">
+        <is>
+          <t>20分</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>練習</t>
+        </is>
+      </c>
+      <c r="E4" s="66" t="inlineStr">
+        <is>
+          <t>フットサル・PKの練習</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="64" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="B5" s="64" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="C5" s="64" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>開会・ルール説明</t>
+        </is>
+      </c>
+      <c r="E5" s="66" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="67" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="C6" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D6" s="68" t="inlineStr">
+        <is>
+          <t>教室対抗戦　準決勝①</t>
+        </is>
+      </c>
+      <c r="E6" s="69" t="inlineStr">
+        <is>
+          <t>フットサル（10分1本・休憩なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="70" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="B7" s="70" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="C7" s="70" t="inlineStr">
+        <is>
+          <t>3分</t>
+        </is>
+      </c>
+      <c r="D7" s="71" t="inlineStr">
+        <is>
+          <t>入れ替え</t>
+        </is>
+      </c>
+      <c r="E7" s="72" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="67" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="B8" s="67" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="C8" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D8" s="68" t="inlineStr">
+        <is>
+          <t>教室対抗戦　準決勝②</t>
+        </is>
+      </c>
+      <c r="E8" s="69" t="inlineStr">
+        <is>
+          <t>フットサル（10分1本・休憩なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="C9" s="70" t="inlineStr">
+        <is>
+          <t>3分</t>
+        </is>
+      </c>
+      <c r="D9" s="71" t="inlineStr">
+        <is>
+          <t>入れ替え</t>
+        </is>
+      </c>
+      <c r="E9" s="72" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C10" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D10" s="68" t="inlineStr">
+        <is>
+          <t>教室対抗戦　決勝</t>
+        </is>
+      </c>
+      <c r="E10" s="69" t="inlineStr">
+        <is>
+          <t>フットサル（10分1本・休憩なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="70" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C11" s="70" t="inlineStr">
+        <is>
+          <t>4分</t>
+        </is>
+      </c>
+      <c r="D11" s="71" t="inlineStr">
+        <is>
+          <t>準備</t>
+        </is>
+      </c>
+      <c r="E11" s="72" t="inlineStr">
+        <is>
+          <t>PK戦のゴール設置など</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="64" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C12" s="64" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D12" s="65" t="inlineStr">
+        <is>
+          <t>休憩</t>
+        </is>
+      </c>
+      <c r="E12" s="66" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="73" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B13" s="73" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C13" s="73" t="inlineStr">
+        <is>
+          <t>8分</t>
+        </is>
+      </c>
+      <c r="D13" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　1回戦（第1・第2試合）</t>
+        </is>
+      </c>
+      <c r="E13" s="75" t="inlineStr">
+        <is>
+          <t>2試合を同時に実施（ゴール2つ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="73" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="B14" s="73" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="C14" s="73" t="inlineStr">
+        <is>
+          <t>8分</t>
+        </is>
+      </c>
+      <c r="D14" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　1回戦（第3試合）</t>
+        </is>
+      </c>
+      <c r="E14" s="75" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="76" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="B15" s="76" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="C15" s="76" t="inlineStr">
+        <is>
+          <t>2分</t>
+        </is>
+      </c>
+      <c r="D15" s="77" t="inlineStr">
+        <is>
+          <t>敗者復活の判定</t>
+        </is>
+      </c>
+      <c r="E15" s="78" t="inlineStr">
+        <is>
+          <t>敗者のうち得失点差が最大のチームを決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="73" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="inlineStr">
+        <is>
+          <t>8分</t>
+        </is>
+      </c>
+      <c r="D16" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　準決勝（2試合）</t>
+        </is>
+      </c>
+      <c r="E16" s="75" t="inlineStr">
+        <is>
+          <t>2試合を同時に実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="73" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="B17" s="73" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="C17" s="73" t="inlineStr">
+        <is>
+          <t>8分</t>
+        </is>
+      </c>
+      <c r="D17" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　決勝</t>
+        </is>
+      </c>
+      <c r="E17" s="75" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="64" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="B18" s="64" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C18" s="64" t="inlineStr">
+        <is>
+          <t>11分</t>
+        </is>
+      </c>
+      <c r="D18" s="65" t="inlineStr">
+        <is>
+          <t>予備・片付け・解散</t>
+        </is>
+      </c>
+      <c r="E18" s="66" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -2224,13 +2224,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="B4" s="64" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C4" s="64" t="inlineStr">
         <is>
-          <t>20分</t>
+          <t>15分</t>
         </is>
       </c>
       <c r="D4" s="65" t="inlineStr">
@@ -2298,12 +2298,12 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="64" t="inlineStr">
         <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B5" s="64" t="inlineStr">
+        <is>
           <t>10:20</t>
-        </is>
-      </c>
-      <c r="B5" s="64" t="inlineStr">
-        <is>
-          <t>10:25</t>
         </is>
       </c>
       <c r="C5" s="64" t="inlineStr">
@@ -2321,12 +2321,12 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="67" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="B6" s="67" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C6" s="67" t="inlineStr">
@@ -2348,12 +2348,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B7" s="70" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="C7" s="70" t="inlineStr">
@@ -2371,12 +2371,12 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="67" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="B8" s="67" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="C8" s="67" t="inlineStr">
@@ -2398,12 +2398,12 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="70" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="B9" s="70" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="C9" s="70" t="inlineStr">
@@ -2421,12 +2421,12 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="67" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="B10" s="67" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="C10" s="67" t="inlineStr">
@@ -2436,214 +2436,291 @@
       </c>
       <c r="D10" s="68" t="inlineStr">
         <is>
-          <t>教室対抗戦　決勝</t>
+          <t>教室対抗戦　3位決定戦</t>
         </is>
       </c>
       <c r="E10" s="69" t="inlineStr">
         <is>
-          <t>フットサル（10分1本・休憩なし）</t>
+          <t>準決勝の敗者どうし</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="70" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="B11" s="70" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="C11" s="70" t="inlineStr">
         <is>
+          <t>3分</t>
+        </is>
+      </c>
+      <c r="D11" s="71" t="inlineStr">
+        <is>
+          <t>入れ替え</t>
+        </is>
+      </c>
+      <c r="E11" s="72" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="B12" s="67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="C12" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D12" s="68" t="inlineStr">
+        <is>
+          <t>教室対抗戦　決勝</t>
+        </is>
+      </c>
+      <c r="E12" s="69" t="inlineStr">
+        <is>
+          <t>フットサル（10分1本・休憩なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="C13" s="70" t="inlineStr">
+        <is>
           <t>4分</t>
         </is>
       </c>
-      <c r="D11" s="71" t="inlineStr">
+      <c r="D13" s="71" t="inlineStr">
         <is>
           <t>準備</t>
         </is>
       </c>
-      <c r="E11" s="72" t="inlineStr">
+      <c r="E13" s="72" t="inlineStr">
         <is>
           <t>PK戦のゴール設置など</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="64" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="B12" s="64" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="C12" s="64" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
-      <c r="D12" s="65" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="64" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D14" s="65" t="inlineStr">
         <is>
           <t>休憩</t>
         </is>
       </c>
-      <c r="E12" s="66" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="73" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B13" s="73" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="C13" s="73" t="inlineStr">
-        <is>
-          <t>8分</t>
-        </is>
-      </c>
-      <c r="D13" s="74" t="inlineStr">
+      <c r="E14" s="66" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="73" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="B15" s="73" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="C15" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D15" s="74" t="inlineStr">
         <is>
           <t>PK戦　1回戦（第1・第2試合）</t>
         </is>
       </c>
-      <c r="E13" s="75" t="inlineStr">
+      <c r="E15" s="75" t="inlineStr">
         <is>
           <t>2試合を同時に実施（ゴール2つ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="73" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="B14" s="73" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="C14" s="73" t="inlineStr">
-        <is>
-          <t>8分</t>
-        </is>
-      </c>
-      <c r="D14" s="74" t="inlineStr">
-        <is>
-          <t>PK戦　1回戦（第3試合）</t>
-        </is>
-      </c>
-      <c r="E14" s="75" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="76" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="B15" s="76" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="C15" s="76" t="inlineStr">
-        <is>
-          <t>2分</t>
-        </is>
-      </c>
-      <c r="D15" s="77" t="inlineStr">
-        <is>
-          <t>敗者復活の判定</t>
-        </is>
-      </c>
-      <c r="E15" s="78" t="inlineStr">
-        <is>
-          <t>敗者のうち得失点差が最大のチームを決定</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="73" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="B16" s="73" t="inlineStr">
         <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D16" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　1回戦（第3試合）</t>
+        </is>
+      </c>
+      <c r="E16" s="75" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="76" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="B17" s="76" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C17" s="76" t="inlineStr">
+        <is>
+          <t>2分</t>
+        </is>
+      </c>
+      <c r="D17" s="77" t="inlineStr">
+        <is>
+          <t>敗者復活の判定</t>
+        </is>
+      </c>
+      <c r="E17" s="78" t="inlineStr">
+        <is>
+          <t>敗者のうち得失点差が最大のチームを決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="73" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="B18" s="73" t="inlineStr">
+        <is>
           <t>11:41</t>
         </is>
       </c>
-      <c r="C16" s="73" t="inlineStr">
-        <is>
-          <t>8分</t>
-        </is>
-      </c>
-      <c r="D16" s="74" t="inlineStr">
+      <c r="C18" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D18" s="74" t="inlineStr">
         <is>
           <t>PK戦　準決勝（2試合）</t>
         </is>
       </c>
-      <c r="E16" s="75" t="inlineStr">
+      <c r="E18" s="75" t="inlineStr">
         <is>
           <t>2試合を同時に実施</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="73" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="73" t="inlineStr">
         <is>
           <t>11:41</t>
         </is>
       </c>
-      <c r="B17" s="73" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="C17" s="73" t="inlineStr">
-        <is>
-          <t>8分</t>
-        </is>
-      </c>
-      <c r="D17" s="74" t="inlineStr">
+      <c r="B19" s="73" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="C19" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D19" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　3位決定戦・5位決定戦</t>
+        </is>
+      </c>
+      <c r="E19" s="75" t="inlineStr">
+        <is>
+          <t>2試合を同時に実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="73" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C20" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D20" s="74" t="inlineStr">
         <is>
           <t>PK戦　決勝</t>
         </is>
       </c>
-      <c r="E17" s="75" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="64" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="B18" s="64" t="inlineStr">
+      <c r="E20" s="75" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="64" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="B21" s="64" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="C18" s="64" t="inlineStr">
-        <is>
-          <t>11分</t>
-        </is>
-      </c>
-      <c r="D18" s="65" t="inlineStr">
+      <c r="C21" s="64" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D21" s="65" t="inlineStr">
         <is>
           <t>予備・片付け・解散</t>
         </is>
       </c>
-      <c r="E18" s="66" t="n"/>
+      <c r="E21" s="66" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -120,6 +120,15 @@
     <font>
       <name val="游ゴシック"/>
       <sz val="15"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <sz val="16"/>
     </font>
   </fonts>
   <fills count="20">
@@ -307,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -522,6 +531,16 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2224,503 +2243,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
-        <is>
-          <t>タイムスケジュール（10:00開始・12:00終了）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="63" t="inlineStr">
-        <is>
-          <t>開始</t>
-        </is>
-      </c>
-      <c r="B3" s="63" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="C3" s="63" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
+        <is>
+          <t>タイムスケジュール</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="80" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="D3" s="63" t="inlineStr">
+      <c r="B3" s="80" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="E3" s="63" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="64" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B4" s="64" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="C4" s="64" t="inlineStr">
-        <is>
-          <t>15分</t>
-        </is>
-      </c>
-      <c r="D4" s="65" t="inlineStr">
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="81" t="inlineStr">
+        <is>
+          <t>10:00–10:15</t>
+        </is>
+      </c>
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>練習</t>
         </is>
       </c>
-      <c r="E4" s="66" t="inlineStr">
-        <is>
-          <t>フットサル・PKの練習</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="64" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B5" s="64" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="C5" s="64" t="inlineStr">
-        <is>
-          <t>5分</t>
-        </is>
-      </c>
-      <c r="D5" s="65" t="inlineStr">
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="81" t="inlineStr">
+        <is>
+          <t>10:15–10:20</t>
+        </is>
+      </c>
+      <c r="B5" s="82" t="inlineStr">
         <is>
           <t>開会・ルール説明</t>
         </is>
       </c>
-      <c r="E5" s="66" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="67" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="B6" s="67" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="C6" s="67" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
-      <c r="D6" s="68" t="inlineStr">
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>10:20–10:30</t>
+        </is>
+      </c>
+      <c r="B6" s="82" t="inlineStr">
         <is>
           <t>教室対抗戦　準決勝①</t>
         </is>
       </c>
-      <c r="E6" s="69" t="inlineStr">
-        <is>
-          <t>フットサル（10分1本・休憩なし）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="70" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B7" s="70" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="C7" s="70" t="inlineStr">
-        <is>
-          <t>3分</t>
-        </is>
-      </c>
-      <c r="D7" s="71" t="inlineStr">
-        <is>
-          <t>入れ替え</t>
-        </is>
-      </c>
-      <c r="E7" s="72" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="67" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="B8" s="67" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="C8" s="67" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
-      <c r="D8" s="68" t="inlineStr">
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>10:33–10:43</t>
+        </is>
+      </c>
+      <c r="B7" s="82" t="inlineStr">
         <is>
           <t>教室対抗戦　準決勝②</t>
         </is>
       </c>
-      <c r="E8" s="69" t="inlineStr">
-        <is>
-          <t>フットサル（10分1本・休憩なし）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="70" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="B9" s="70" t="inlineStr">
-        <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="C9" s="70" t="inlineStr">
-        <is>
-          <t>3分</t>
-        </is>
-      </c>
-      <c r="D9" s="71" t="inlineStr">
-        <is>
-          <t>入れ替え</t>
-        </is>
-      </c>
-      <c r="E9" s="72" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="67" t="inlineStr">
-        <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="B10" s="67" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="C10" s="67" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
-      <c r="D10" s="68" t="inlineStr">
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="81" t="inlineStr">
+        <is>
+          <t>10:46–10:56</t>
+        </is>
+      </c>
+      <c r="B8" s="82" t="inlineStr">
         <is>
           <t>教室対抗戦　3位決定戦</t>
         </is>
       </c>
-      <c r="E10" s="69" t="inlineStr">
-        <is>
-          <t>準決勝の敗者どうし</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="70" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="B11" s="70" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="C11" s="70" t="inlineStr">
-        <is>
-          <t>3分</t>
-        </is>
-      </c>
-      <c r="D11" s="71" t="inlineStr">
-        <is>
-          <t>入れ替え</t>
-        </is>
-      </c>
-      <c r="E11" s="72" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="67" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="B12" s="67" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="C12" s="67" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
-      <c r="D12" s="68" t="inlineStr">
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="81" t="inlineStr">
+        <is>
+          <t>10:59–11:09</t>
+        </is>
+      </c>
+      <c r="B9" s="82" t="inlineStr">
         <is>
           <t>教室対抗戦　決勝</t>
         </is>
       </c>
-      <c r="E12" s="69" t="inlineStr">
-        <is>
-          <t>フットサル（10分1本・休憩なし）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="70" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="B13" s="70" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="C13" s="70" t="inlineStr">
-        <is>
-          <t>4分</t>
-        </is>
-      </c>
-      <c r="D13" s="71" t="inlineStr">
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="81" t="inlineStr">
+        <is>
+          <t>11:09–11:13</t>
+        </is>
+      </c>
+      <c r="B10" s="82" t="inlineStr">
         <is>
           <t>準備</t>
         </is>
       </c>
-      <c r="E13" s="72" t="inlineStr">
-        <is>
-          <t>PK戦のゴール設置など</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="64" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="B14" s="64" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="C14" s="64" t="inlineStr">
-        <is>
-          <t>5分</t>
-        </is>
-      </c>
-      <c r="D14" s="65" t="inlineStr">
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="81" t="inlineStr">
+        <is>
+          <t>11:13–11:18</t>
+        </is>
+      </c>
+      <c r="B11" s="82" t="inlineStr">
         <is>
           <t>休憩</t>
         </is>
       </c>
-      <c r="E14" s="66" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="73" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="B15" s="73" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="C15" s="73" t="inlineStr">
-        <is>
-          <t>7分</t>
-        </is>
-      </c>
-      <c r="D15" s="74" t="inlineStr">
-        <is>
-          <t>PK戦　1回戦（第1・第2試合）</t>
-        </is>
-      </c>
-      <c r="E15" s="75" t="inlineStr">
-        <is>
-          <t>2試合を同時に実施（ゴール2つ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="73" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="B16" s="73" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="C16" s="73" t="inlineStr">
-        <is>
-          <t>7分</t>
-        </is>
-      </c>
-      <c r="D16" s="74" t="inlineStr">
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="81" t="inlineStr">
+        <is>
+          <t>11:18–11:25</t>
+        </is>
+      </c>
+      <c r="B12" s="82" t="inlineStr">
+        <is>
+          <t>PK戦　1回戦（第1・第2試合を同時に）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="81" t="inlineStr">
+        <is>
+          <t>11:25–11:32</t>
+        </is>
+      </c>
+      <c r="B13" s="82" t="inlineStr">
         <is>
           <t>PK戦　1回戦（第3試合）</t>
         </is>
       </c>
-      <c r="E16" s="75" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="76" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="B17" s="76" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="C17" s="76" t="inlineStr">
-        <is>
-          <t>2分</t>
-        </is>
-      </c>
-      <c r="D17" s="77" t="inlineStr">
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="81" t="inlineStr">
+        <is>
+          <t>11:32–11:34</t>
+        </is>
+      </c>
+      <c r="B14" s="82" t="inlineStr">
         <is>
           <t>敗者復活の判定</t>
         </is>
       </c>
-      <c r="E17" s="78" t="inlineStr">
-        <is>
-          <t>敗者のうち得失点差が最大のチームを決定</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="73" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="B18" s="73" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="C18" s="73" t="inlineStr">
-        <is>
-          <t>7分</t>
-        </is>
-      </c>
-      <c r="D18" s="74" t="inlineStr">
-        <is>
-          <t>PK戦　準決勝（2試合）</t>
-        </is>
-      </c>
-      <c r="E18" s="75" t="inlineStr">
-        <is>
-          <t>2試合を同時に実施</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="73" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="B19" s="73" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="C19" s="73" t="inlineStr">
-        <is>
-          <t>7分</t>
-        </is>
-      </c>
-      <c r="D19" s="74" t="inlineStr">
-        <is>
-          <t>PK戦　3位決定戦・5位決定戦</t>
-        </is>
-      </c>
-      <c r="E19" s="75" t="inlineStr">
-        <is>
-          <t>2試合を同時に実施</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="73" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="B20" s="73" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="C20" s="73" t="inlineStr">
-        <is>
-          <t>7分</t>
-        </is>
-      </c>
-      <c r="D20" s="74" t="inlineStr">
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="81" t="inlineStr">
+        <is>
+          <t>11:34–11:41</t>
+        </is>
+      </c>
+      <c r="B15" s="82" t="inlineStr">
+        <is>
+          <t>PK戦　準決勝（2試合を同時に）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="81" t="inlineStr">
+        <is>
+          <t>11:41–11:48</t>
+        </is>
+      </c>
+      <c r="B16" s="82" t="inlineStr">
+        <is>
+          <t>PK戦　3位決定戦</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="81" t="inlineStr">
+        <is>
+          <t>11:48–11:55</t>
+        </is>
+      </c>
+      <c r="B17" s="82" t="inlineStr">
         <is>
           <t>PK戦　決勝</t>
         </is>
       </c>
-      <c r="E20" s="75" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="64" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="B21" s="64" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C21" s="64" t="inlineStr">
-        <is>
-          <t>5分</t>
-        </is>
-      </c>
-      <c r="D21" s="65" t="inlineStr">
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="81" t="inlineStr">
+        <is>
+          <t>11:55–12:00</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="inlineStr">
         <is>
           <t>予備・片付け・解散</t>
         </is>
       </c>
-      <c r="E21" s="66" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -2243,214 +2243,503 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="79" t="inlineStr">
-        <is>
-          <t>タイムスケジュール</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="80" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>タイムスケジュール（10:00開始・12:00終了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="63" t="inlineStr">
+        <is>
+          <t>開始</t>
+        </is>
+      </c>
+      <c r="B3" s="63" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="C3" s="63" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="B3" s="80" t="inlineStr">
+      <c r="D3" s="63" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="81" t="inlineStr">
-        <is>
-          <t>10:00–10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="82" t="inlineStr">
+      <c r="E3" s="63" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="64" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B4" s="64" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C4" s="64" t="inlineStr">
+        <is>
+          <t>15分</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
         <is>
           <t>練習</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="81" t="inlineStr">
-        <is>
-          <t>10:15–10:20</t>
-        </is>
-      </c>
-      <c r="B5" s="82" t="inlineStr">
+      <c r="E4" s="66" t="inlineStr">
+        <is>
+          <t>フットサル・PKの練習</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="64" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B5" s="64" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C5" s="64" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
         <is>
           <t>開会・ルール説明</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="81" t="inlineStr">
-        <is>
-          <t>10:20–10:30</t>
-        </is>
-      </c>
-      <c r="B6" s="82" t="inlineStr">
+      <c r="E5" s="66" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="67" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C6" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D6" s="68" t="inlineStr">
         <is>
           <t>教室対抗戦　準決勝①</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="81" t="inlineStr">
-        <is>
-          <t>10:33–10:43</t>
-        </is>
-      </c>
-      <c r="B7" s="82" t="inlineStr">
+      <c r="E6" s="69" t="inlineStr">
+        <is>
+          <t>フットサル（10分1本・休憩なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="70" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="B7" s="70" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C7" s="70" t="inlineStr">
+        <is>
+          <t>3分</t>
+        </is>
+      </c>
+      <c r="D7" s="71" t="inlineStr">
+        <is>
+          <t>入れ替え</t>
+        </is>
+      </c>
+      <c r="E7" s="72" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="67" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="B8" s="67" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="C8" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D8" s="68" t="inlineStr">
         <is>
           <t>教室対抗戦　準決勝②</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="81" t="inlineStr">
-        <is>
-          <t>10:46–10:56</t>
-        </is>
-      </c>
-      <c r="B8" s="82" t="inlineStr">
+      <c r="E8" s="69" t="inlineStr">
+        <is>
+          <t>フットサル（10分1本・休憩なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C9" s="70" t="inlineStr">
+        <is>
+          <t>3分</t>
+        </is>
+      </c>
+      <c r="D9" s="71" t="inlineStr">
+        <is>
+          <t>入れ替え</t>
+        </is>
+      </c>
+      <c r="E9" s="72" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C10" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D10" s="68" t="inlineStr">
         <is>
           <t>教室対抗戦　3位決定戦</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="81" t="inlineStr">
-        <is>
-          <t>10:59–11:09</t>
-        </is>
-      </c>
-      <c r="B9" s="82" t="inlineStr">
+      <c r="E10" s="69" t="inlineStr">
+        <is>
+          <t>準決勝の敗者どうし</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="70" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="C11" s="70" t="inlineStr">
+        <is>
+          <t>3分</t>
+        </is>
+      </c>
+      <c r="D11" s="71" t="inlineStr">
+        <is>
+          <t>入れ替え</t>
+        </is>
+      </c>
+      <c r="E11" s="72" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="B12" s="67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="C12" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D12" s="68" t="inlineStr">
         <is>
           <t>教室対抗戦　決勝</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="81" t="inlineStr">
-        <is>
-          <t>11:09–11:13</t>
-        </is>
-      </c>
-      <c r="B10" s="82" t="inlineStr">
+      <c r="E12" s="69" t="inlineStr">
+        <is>
+          <t>フットサル（10分1本・休憩なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="C13" s="70" t="inlineStr">
+        <is>
+          <t>4分</t>
+        </is>
+      </c>
+      <c r="D13" s="71" t="inlineStr">
         <is>
           <t>準備</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="81" t="inlineStr">
-        <is>
-          <t>11:13–11:18</t>
-        </is>
-      </c>
-      <c r="B11" s="82" t="inlineStr">
+      <c r="E13" s="72" t="inlineStr">
+        <is>
+          <t>PK戦のゴール設置など</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="64" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D14" s="65" t="inlineStr">
         <is>
           <t>休憩</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="81" t="inlineStr">
-        <is>
-          <t>11:18–11:25</t>
-        </is>
-      </c>
-      <c r="B12" s="82" t="inlineStr">
-        <is>
-          <t>PK戦　1回戦（第1・第2試合を同時に）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="81" t="inlineStr">
-        <is>
-          <t>11:25–11:32</t>
-        </is>
-      </c>
-      <c r="B13" s="82" t="inlineStr">
+      <c r="E14" s="66" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="73" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="B15" s="73" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="C15" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D15" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　1回戦（第1・第2試合）</t>
+        </is>
+      </c>
+      <c r="E15" s="75" t="inlineStr">
+        <is>
+          <t>2試合を同時に実施（ゴール2つ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="73" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D16" s="74" t="inlineStr">
         <is>
           <t>PK戦　1回戦（第3試合）</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="81" t="inlineStr">
-        <is>
-          <t>11:32–11:34</t>
-        </is>
-      </c>
-      <c r="B14" s="82" t="inlineStr">
+      <c r="E16" s="75" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="76" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="B17" s="76" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C17" s="76" t="inlineStr">
+        <is>
+          <t>2分</t>
+        </is>
+      </c>
+      <c r="D17" s="77" t="inlineStr">
         <is>
           <t>敗者復活の判定</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="81" t="inlineStr">
-        <is>
-          <t>11:34–11:41</t>
-        </is>
-      </c>
-      <c r="B15" s="82" t="inlineStr">
-        <is>
-          <t>PK戦　準決勝（2試合を同時に）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="81" t="inlineStr">
-        <is>
-          <t>11:41–11:48</t>
-        </is>
-      </c>
-      <c r="B16" s="82" t="inlineStr">
+      <c r="E17" s="78" t="inlineStr">
+        <is>
+          <t>敗者のうち得失点差が最大のチームを決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="73" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="B18" s="73" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="C18" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D18" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　準決勝（2試合）</t>
+        </is>
+      </c>
+      <c r="E18" s="75" t="inlineStr">
+        <is>
+          <t>2試合を同時に実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="73" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="B19" s="73" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="C19" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D19" s="74" t="inlineStr">
         <is>
           <t>PK戦　3位決定戦</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="81" t="inlineStr">
-        <is>
-          <t>11:48–11:55</t>
-        </is>
-      </c>
-      <c r="B17" s="82" t="inlineStr">
+      <c r="E19" s="75" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="73" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C20" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D20" s="74" t="inlineStr">
         <is>
           <t>PK戦　決勝</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="81" t="inlineStr">
-        <is>
-          <t>11:55–12:00</t>
-        </is>
-      </c>
-      <c r="B18" s="82" t="inlineStr">
+      <c r="E20" s="75" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="64" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="B21" s="64" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C21" s="64" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D21" s="65" t="inlineStr">
         <is>
           <t>予備・片付け・解散</t>
         </is>
       </c>
+      <c r="E21" s="66" t="n"/>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/互助会レクリエーション.xlsx
+++ b/互助会レクリエーション.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教科事務対抗PK戦" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="景品リスト" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タイムスケジュール" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タイムスケジュール(20分押し)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2742,4 +2743,511 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>タイムスケジュール（20分押し：10:20開始・12:20終了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="63" t="inlineStr">
+        <is>
+          <t>開始</t>
+        </is>
+      </c>
+      <c r="B3" s="63" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="C3" s="63" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="D3" s="63" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E3" s="63" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="64" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="B4" s="64" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="C4" s="64" t="inlineStr">
+        <is>
+          <t>15分</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>練習</t>
+        </is>
+      </c>
+      <c r="E4" s="66" t="inlineStr">
+        <is>
+          <t>フットサル・PKの練習</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="64" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="B5" s="64" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="C5" s="64" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>開会・ルール説明</t>
+        </is>
+      </c>
+      <c r="E5" s="66" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="67" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="C6" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D6" s="68" t="inlineStr">
+        <is>
+          <t>教室対抗戦　準決勝①</t>
+        </is>
+      </c>
+      <c r="E6" s="69" t="inlineStr">
+        <is>
+          <t>フットサル（10分1本・休憩なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="70" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="B7" s="70" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="C7" s="70" t="inlineStr">
+        <is>
+          <t>3分</t>
+        </is>
+      </c>
+      <c r="D7" s="71" t="inlineStr">
+        <is>
+          <t>入れ替え</t>
+        </is>
+      </c>
+      <c r="E7" s="72" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="67" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="B8" s="67" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C8" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D8" s="68" t="inlineStr">
+        <is>
+          <t>教室対抗戦　準決勝②</t>
+        </is>
+      </c>
+      <c r="E8" s="69" t="inlineStr">
+        <is>
+          <t>フットサル（10分1本・休憩なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C9" s="70" t="inlineStr">
+        <is>
+          <t>3分</t>
+        </is>
+      </c>
+      <c r="D9" s="71" t="inlineStr">
+        <is>
+          <t>入れ替え</t>
+        </is>
+      </c>
+      <c r="E9" s="72" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="C10" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D10" s="68" t="inlineStr">
+        <is>
+          <t>教室対抗戦　3位決定戦</t>
+        </is>
+      </c>
+      <c r="E10" s="69" t="inlineStr">
+        <is>
+          <t>準決勝の敗者どうし</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="70" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="C11" s="70" t="inlineStr">
+        <is>
+          <t>3分</t>
+        </is>
+      </c>
+      <c r="D11" s="71" t="inlineStr">
+        <is>
+          <t>入れ替え</t>
+        </is>
+      </c>
+      <c r="E11" s="72" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="B12" s="67" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="C12" s="67" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D12" s="68" t="inlineStr">
+        <is>
+          <t>教室対抗戦　決勝</t>
+        </is>
+      </c>
+      <c r="E12" s="69" t="inlineStr">
+        <is>
+          <t>フットサル（10分1本・休憩なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="C13" s="70" t="inlineStr">
+        <is>
+          <t>4分</t>
+        </is>
+      </c>
+      <c r="D13" s="71" t="inlineStr">
+        <is>
+          <t>準備</t>
+        </is>
+      </c>
+      <c r="E13" s="72" t="inlineStr">
+        <is>
+          <t>PK戦のゴール設置など</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="64" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D14" s="65" t="inlineStr">
+        <is>
+          <t>休憩</t>
+        </is>
+      </c>
+      <c r="E14" s="66" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="73" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="B15" s="73" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C15" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D15" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　1回戦（第1・第2試合）</t>
+        </is>
+      </c>
+      <c r="E15" s="75" t="inlineStr">
+        <is>
+          <t>2試合を同時に実施（ゴール2つ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="73" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D16" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　1回戦（第3試合）</t>
+        </is>
+      </c>
+      <c r="E16" s="75" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="76" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="B17" s="76" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="C17" s="76" t="inlineStr">
+        <is>
+          <t>2分</t>
+        </is>
+      </c>
+      <c r="D17" s="77" t="inlineStr">
+        <is>
+          <t>敗者復活の判定</t>
+        </is>
+      </c>
+      <c r="E17" s="78" t="inlineStr">
+        <is>
+          <t>敗者のうち得失点差が最大のチームを決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="73" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="B18" s="73" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="C18" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D18" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　準決勝（2試合）</t>
+        </is>
+      </c>
+      <c r="E18" s="75" t="inlineStr">
+        <is>
+          <t>2試合を同時に実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="73" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="B19" s="73" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="C19" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D19" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　3位決定戦</t>
+        </is>
+      </c>
+      <c r="E19" s="75" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="73" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C20" s="73" t="inlineStr">
+        <is>
+          <t>7分</t>
+        </is>
+      </c>
+      <c r="D20" s="74" t="inlineStr">
+        <is>
+          <t>PK戦　決勝</t>
+        </is>
+      </c>
+      <c r="E20" s="75" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="64" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="B21" s="64" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C21" s="64" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="D21" s="65" t="inlineStr">
+        <is>
+          <t>予備・片付け・解散</t>
+        </is>
+      </c>
+      <c r="E21" s="66" t="n"/>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>